--- a/analysis/main_tables/r2_table.xlsx
+++ b/analysis/main_tables/r2_table.xlsx
@@ -460,10 +460,10 @@
         <v>0.383690867423742</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5885366722060511</v>
+        <v>0.5885366722060508</v>
       </c>
       <c r="D2" t="n">
-        <v>0.624070185767616</v>
+        <v>0.5914468785146928</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>0.7153750795101295</v>
       </c>
       <c r="D3" t="n">
-        <v>0.756115557185981</v>
+        <v>0.7187664039301185</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>0.5839556571583073</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7400733070297351</v>
+        <v>0.7400733070297357</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7723375754511835</v>
+        <v>0.7434380683738435</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>0.70508059263889</v>
       </c>
       <c r="C5" t="n">
-        <v>0.782231996944451</v>
+        <v>0.7822319969444516</v>
       </c>
       <c r="D5" t="n">
-        <v>0.806745011545474</v>
+        <v>0.7857354348774375</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>0.6762333735971855</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8036599213638229</v>
+        <v>0.8036599213638219</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8139452667649676</v>
+        <v>0.8066501015898672</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>0.7642292533357955</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7644707871401335</v>
+        <v>0.7656324417913569</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         <v>0.3489329440777856</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5310264851532205</v>
+        <v>0.53102648515322</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5929073685334815</v>
+        <v>0.5347842749825662</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         <v>0.6711544708168184</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8095504252942273</v>
+        <v>0.8095504252942268</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8591659210976874</v>
+        <v>0.8140975457396832</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>0.6718257107122056</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8256183584309909</v>
+        <v>0.825618358430992</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8497227725840172</v>
+        <v>0.8293843650167247</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>0.630702305193605</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8624775248763458</v>
+        <v>0.8624775248763452</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8691138878060121</v>
+        <v>0.8646703384810646</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         <v>0.5929561520683952</v>
       </c>
       <c r="C12" t="n">
-        <v>0.841212927430945</v>
+        <v>0.8412129274309452</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8434796649577093</v>
+        <v>0.8432992926473709</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>0.2397931173600915</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3745277775290248</v>
+        <v>0.3745277775290246</v>
       </c>
       <c r="D13" t="n">
-        <v>0.496220794737644</v>
+        <v>0.3778776523422254</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         <v>0.287254439769119</v>
       </c>
       <c r="C14" t="n">
-        <v>0.381057181492149</v>
+        <v>0.3810571814921489</v>
       </c>
       <c r="D14" t="n">
-        <v>0.549336610635078</v>
+        <v>0.3844171117543342</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +668,10 @@
         <v>0.3550028210253486</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4301879219231377</v>
+        <v>0.4301879219231376</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5848256037548677</v>
+        <v>0.4338813760968098</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         <v>0.4540115432610878</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5218989987117629</v>
+        <v>0.5218989987117625</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6113561207258259</v>
+        <v>0.5259638817785133</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         <v>0.5242519742001892</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7006157380279142</v>
+        <v>0.7006157380279131</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7586845960231761</v>
+        <v>0.7049694856586144</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +716,10 @@
         <v>0.5737639603577718</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7987559504120979</v>
+        <v>0.7987559504120982</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8352175076561613</v>
+        <v>0.8025824809338078</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>0.6306595907673235</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8446767808088257</v>
+        <v>0.8446767808088249</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8662664386832915</v>
+        <v>0.8482410639547229</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>0.6371240819909557</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8554446488756218</v>
+        <v>0.8554446488756207</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8652161582416737</v>
+        <v>0.8587576421472526</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>0.6020154158319817</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8534228964415241</v>
+        <v>0.8534228964415246</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8584341219557329</v>
+        <v>0.8562413837773374</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6409382230977771</v>
+        <v>0.6412372970886957</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7604217987621019</v>
+        <v>0.76182750160554</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8387172441999282</v>
+        <v>0.7669477731529121</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7101341576805366</v>
+        <v>0.7102506966638465</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7940850890904245</v>
+        <v>0.7780498887053863</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8476824226826389</v>
+        <v>0.7820202634660472</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7838582598485035</v>
+        <v>0.7840719584357971</v>
       </c>
       <c r="C24" t="n">
-        <v>0.847207712774909</v>
+        <v>0.8365716961611958</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8550880163505568</v>
+        <v>0.8390041846626251</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6610195239634022</v>
+        <v>0.6611963467765015</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8164806074401034</v>
+        <v>0.8074786585497478</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8200198151017841</v>
+        <v>0.8095381824244459</v>
       </c>
     </row>
   </sheetData>
